--- a/public/static/colorMode.xlsx
+++ b/public/static/colorMode.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\0移动C盘\下载\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1桌面\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="info" sheetId="1" r:id="rId1"/>
     <sheet name="venue" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet name="type" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="type" sheetId="3" r:id="rId3"/>
     <sheet name="color" sheetId="4" state="hidden" r:id="rId4"/>
     <sheet name="state" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
@@ -1682,13 +1682,13 @@
     <t>浙江省温州市瓯海区南白象街道鹅湖村</t>
   </si>
   <si>
-    <t>消防安全</t>
-  </si>
-  <si>
-    <t>地质灾害</t>
-  </si>
-  <si>
-    <t>违章违法</t>
+    <t>场所安全</t>
+  </si>
+  <si>
+    <t>涉宗案件</t>
+  </si>
+  <si>
+    <t>规范管理</t>
   </si>
   <si>
     <t>投诉举报</t>
@@ -1697,7 +1697,7 @@
     <t>重点场所</t>
   </si>
   <si>
-    <t>建筑安全</t>
+    <t>重点工作</t>
   </si>
   <si>
     <t>红</t>
@@ -7517,7 +7517,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="b5xG6S50YNdu5vcDsdxk9yVyogsybsDK10xPOCC3J/PiIlOOIk2b1KHBdax9C0JUbbJP4+RBMkh4FphX/owIag==" saltValue="7lE62mSy2wBuYZuuvvzV4w==" spinCount="100000" sheet="1" objects="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="xsOmXkHveB4JhJsnvT4kpPwRMReV5BT3vCejhuK5l25e6RcaeM3TWGrUufPFCpGKtHgo0HdI4yTcK5vCwFpv2w==" saltValue="m9jJ287xcofTH5b5xpNhGA==" spinCount="100000" sheet="1" objects="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/public/static/colorMode.xlsx
+++ b/public/static/colorMode.xlsx
@@ -2,12 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1桌面\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="z+W/lf/4bzS9y1A/ktUgwd4lbldOTu09BIaHK/gbNeTWTUZJjScn/URY7BO7NY7GpAiMoJKNYw+EbyOiojhZDw==" workbookSaltValue="mYty5RqI2vhCDxvanrnDbA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
@@ -59,7 +60,8 @@
     <t>coColor</t>
   </si>
   <si>
-    <t>发生时间</t>
+    <t>发生时间
+2026/01/01</t>
   </si>
   <si>
     <t>问题描述</t>
@@ -71,7 +73,8 @@
     <t>coState</t>
   </si>
   <si>
-    <t>完成时间</t>
+    <t>完成时间
+2026/01/01</t>
   </si>
   <si>
     <t>进度描述</t>
@@ -1682,22 +1685,22 @@
     <t>浙江省温州市瓯海区南白象街道鹅湖村</t>
   </si>
   <si>
+    <t>重点场所</t>
+  </si>
+  <si>
+    <t>涉宗案件</t>
+  </si>
+  <si>
+    <t>投诉举报</t>
+  </si>
+  <si>
+    <t>重点工作</t>
+  </si>
+  <si>
     <t>场所安全</t>
   </si>
   <si>
-    <t>涉宗案件</t>
-  </si>
-  <si>
     <t>规范管理</t>
-  </si>
-  <si>
-    <t>投诉举报</t>
-  </si>
-  <si>
-    <t>重点场所</t>
-  </si>
-  <si>
-    <t>重点工作</t>
   </si>
   <si>
     <t>红</t>
@@ -1731,13 +1734,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy\-m\-d\ hh:mm:ss"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -2378,6 +2380,10 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -2395,11 +2401,7 @@
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
@@ -2929,7 +2931,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:N59"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
@@ -2940,56 +2942,56 @@
     <col min="5" max="5" width="0.222222222222222" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="10.1111111111111" style="5" customWidth="1"/>
     <col min="7" max="7" width="8.88888888888889" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="19.7777777777778" style="5" customWidth="1"/>
+    <col min="8" max="8" width="19.8888888888889" style="6" customWidth="1"/>
     <col min="9" max="9" width="50.1111111111111" style="4" customWidth="1"/>
     <col min="10" max="10" width="10.2222222222222" style="5" customWidth="1"/>
     <col min="11" max="11" width="0.222222222222222" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="20.2222222222222" style="5" customWidth="1"/>
+    <col min="12" max="12" width="21.2222222222222" style="6" customWidth="1"/>
     <col min="13" max="13" width="33.6666666666667" style="4" customWidth="1"/>
     <col min="14" max="14" width="16.6666666666667" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="1" ht="25" customHeight="1" spans="1:14">
-      <c r="A1" s="6" t="s">
+    <row r="1" s="3" customFormat="1" ht="54" customHeight="1" spans="1:14">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3010,12 +3012,10 @@
         <f>IFERROR(VLOOKUP(F2,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H2" s="11"/>
       <c r="K2" t="str">
         <f>IFERROR(VLOOKUP(J2,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L2" s="11"/>
     </row>
     <row r="3" spans="1:14">
       <c r="B3" t="str">
@@ -3034,12 +3034,10 @@
         <f>IFERROR(VLOOKUP(F3,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H3" s="11"/>
       <c r="K3" t="str">
         <f>IFERROR(VLOOKUP(J3,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L3" s="11"/>
     </row>
     <row r="4" spans="1:14">
       <c r="B4" t="str">
@@ -3058,12 +3056,10 @@
         <f>IFERROR(VLOOKUP(F4,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H4" s="11"/>
       <c r="K4" t="str">
         <f>IFERROR(VLOOKUP(J4,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L4" s="11"/>
     </row>
     <row r="5" spans="1:14">
       <c r="B5" t="str">
@@ -3082,12 +3078,10 @@
         <f>IFERROR(VLOOKUP(F5,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H5" s="11"/>
       <c r="K5" t="str">
         <f>IFERROR(VLOOKUP(J5,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L5" s="11"/>
     </row>
     <row r="6" spans="1:14">
       <c r="B6" t="str">
@@ -3106,12 +3100,10 @@
         <f>IFERROR(VLOOKUP(F6,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H6" s="11"/>
       <c r="K6" t="str">
         <f>IFERROR(VLOOKUP(J6,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L6" s="11"/>
     </row>
     <row r="7" spans="1:14">
       <c r="B7" t="str">
@@ -3130,12 +3122,10 @@
         <f>IFERROR(VLOOKUP(F7,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H7" s="11"/>
       <c r="K7" t="str">
         <f>IFERROR(VLOOKUP(J7,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L7" s="11"/>
     </row>
     <row r="8" spans="1:14">
       <c r="B8" t="str">
@@ -3154,12 +3144,10 @@
         <f>IFERROR(VLOOKUP(F8,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H8" s="11"/>
       <c r="K8" t="str">
         <f>IFERROR(VLOOKUP(J8,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L8" s="11"/>
     </row>
     <row r="9" spans="1:14">
       <c r="B9" t="str">
@@ -3178,12 +3166,10 @@
         <f>IFERROR(VLOOKUP(F9,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H9" s="11"/>
       <c r="K9" t="str">
         <f>IFERROR(VLOOKUP(J9,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L9" s="11"/>
     </row>
     <row r="10" spans="1:14">
       <c r="B10" t="str">
@@ -3202,12 +3188,10 @@
         <f>IFERROR(VLOOKUP(F10,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H10" s="11"/>
       <c r="K10" t="str">
         <f>IFERROR(VLOOKUP(J10,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L10" s="11"/>
     </row>
     <row r="11" spans="1:14">
       <c r="B11" t="str">
@@ -3226,12 +3210,10 @@
         <f>IFERROR(VLOOKUP(F11,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H11" s="11"/>
       <c r="K11" t="str">
         <f>IFERROR(VLOOKUP(J11,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L11" s="11"/>
     </row>
     <row r="12" spans="1:14">
       <c r="B12" t="str">
@@ -3250,12 +3232,10 @@
         <f>IFERROR(VLOOKUP(F12,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H12" s="11"/>
       <c r="K12" t="str">
         <f>IFERROR(VLOOKUP(J12,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L12" s="11"/>
     </row>
     <row r="13" spans="1:14">
       <c r="B13" t="str">
@@ -3274,12 +3254,10 @@
         <f>IFERROR(VLOOKUP(F13,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H13" s="11"/>
       <c r="K13" t="str">
         <f>IFERROR(VLOOKUP(J13,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L13" s="11"/>
     </row>
     <row r="14" spans="1:14">
       <c r="B14" t="str">
@@ -3298,12 +3276,10 @@
         <f>IFERROR(VLOOKUP(F14,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H14" s="11"/>
       <c r="K14" t="str">
         <f>IFERROR(VLOOKUP(J14,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L14" s="11"/>
     </row>
     <row r="15" spans="1:14">
       <c r="B15" t="str">
@@ -3322,12 +3298,10 @@
         <f>IFERROR(VLOOKUP(F15,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H15" s="11"/>
       <c r="K15" t="str">
         <f>IFERROR(VLOOKUP(J15,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L15" s="11"/>
     </row>
     <row r="16" spans="1:14">
       <c r="B16" t="str">
@@ -3346,14 +3320,12 @@
         <f>IFERROR(VLOOKUP(F16,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H16" s="11"/>
       <c r="K16" t="str">
         <f>IFERROR(VLOOKUP(J16,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L16" s="11"/>
-    </row>
-    <row r="17" spans="2:12">
+    </row>
+    <row r="17" spans="2:11">
       <c r="B17" t="str">
         <f>IFERROR(VLOOKUP(A17,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3370,14 +3342,12 @@
         <f>IFERROR(VLOOKUP(F17,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H17" s="11"/>
       <c r="K17" t="str">
         <f>IFERROR(VLOOKUP(J17,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L17" s="11"/>
-    </row>
-    <row r="18" spans="2:12">
+    </row>
+    <row r="18" spans="2:11">
       <c r="B18" t="str">
         <f>IFERROR(VLOOKUP(A18,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3394,14 +3364,12 @@
         <f>IFERROR(VLOOKUP(F18,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H18" s="11"/>
       <c r="K18" t="str">
         <f>IFERROR(VLOOKUP(J18,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L18" s="11"/>
-    </row>
-    <row r="19" spans="2:12">
+    </row>
+    <row r="19" spans="2:11">
       <c r="B19" t="str">
         <f>IFERROR(VLOOKUP(A19,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3418,14 +3386,12 @@
         <f>IFERROR(VLOOKUP(F19,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H19" s="11"/>
       <c r="K19" t="str">
         <f>IFERROR(VLOOKUP(J19,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L19" s="11"/>
-    </row>
-    <row r="20" spans="2:12">
+    </row>
+    <row r="20" spans="2:11">
       <c r="B20" t="str">
         <f>IFERROR(VLOOKUP(A20,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3442,14 +3408,12 @@
         <f>IFERROR(VLOOKUP(F20,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H20" s="11"/>
       <c r="K20" t="str">
         <f>IFERROR(VLOOKUP(J20,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L20" s="11"/>
-    </row>
-    <row r="21" spans="2:12">
+    </row>
+    <row r="21" spans="2:11">
       <c r="B21" t="str">
         <f>IFERROR(VLOOKUP(A21,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3466,14 +3430,12 @@
         <f>IFERROR(VLOOKUP(F21,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H21" s="11"/>
       <c r="K21" t="str">
         <f>IFERROR(VLOOKUP(J21,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L21" s="11"/>
-    </row>
-    <row r="22" spans="2:12">
+    </row>
+    <row r="22" spans="2:11">
       <c r="B22" t="str">
         <f>IFERROR(VLOOKUP(A22,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3490,14 +3452,12 @@
         <f>IFERROR(VLOOKUP(F22,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H22" s="11"/>
       <c r="K22" t="str">
         <f>IFERROR(VLOOKUP(J22,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L22" s="11"/>
-    </row>
-    <row r="23" spans="2:12">
+    </row>
+    <row r="23" spans="2:11">
       <c r="B23" t="str">
         <f>IFERROR(VLOOKUP(A23,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3514,14 +3474,12 @@
         <f>IFERROR(VLOOKUP(F23,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H23" s="11"/>
       <c r="K23" t="str">
         <f>IFERROR(VLOOKUP(J23,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L23" s="11"/>
-    </row>
-    <row r="24" spans="2:12">
+    </row>
+    <row r="24" spans="2:11">
       <c r="B24" t="str">
         <f>IFERROR(VLOOKUP(A24,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3538,14 +3496,12 @@
         <f>IFERROR(VLOOKUP(F24,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H24" s="11"/>
       <c r="K24" t="str">
         <f>IFERROR(VLOOKUP(J24,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L24" s="11"/>
-    </row>
-    <row r="25" spans="2:12">
+    </row>
+    <row r="25" spans="2:11">
       <c r="B25" t="str">
         <f>IFERROR(VLOOKUP(A25,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3562,14 +3518,12 @@
         <f>IFERROR(VLOOKUP(F25,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H25" s="11"/>
       <c r="K25" t="str">
         <f>IFERROR(VLOOKUP(J25,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L25" s="11"/>
-    </row>
-    <row r="26" spans="2:12">
+    </row>
+    <row r="26" spans="2:11">
       <c r="B26" t="str">
         <f>IFERROR(VLOOKUP(A26,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3586,14 +3540,12 @@
         <f>IFERROR(VLOOKUP(F26,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H26" s="11"/>
       <c r="K26" t="str">
         <f>IFERROR(VLOOKUP(J26,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L26" s="11"/>
-    </row>
-    <row r="27" spans="2:12">
+    </row>
+    <row r="27" spans="2:11">
       <c r="B27" t="str">
         <f>IFERROR(VLOOKUP(A27,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3610,14 +3562,12 @@
         <f>IFERROR(VLOOKUP(F27,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H27" s="11"/>
       <c r="K27" t="str">
         <f>IFERROR(VLOOKUP(J27,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L27" s="11"/>
-    </row>
-    <row r="28" spans="2:12">
+    </row>
+    <row r="28" spans="2:11">
       <c r="B28" t="str">
         <f>IFERROR(VLOOKUP(A28,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3634,14 +3584,12 @@
         <f>IFERROR(VLOOKUP(F28,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H28" s="11"/>
       <c r="K28" t="str">
         <f>IFERROR(VLOOKUP(J28,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L28" s="11"/>
-    </row>
-    <row r="29" spans="2:12">
+    </row>
+    <row r="29" spans="2:11">
       <c r="B29" t="str">
         <f>IFERROR(VLOOKUP(A29,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3658,14 +3606,12 @@
         <f>IFERROR(VLOOKUP(F29,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H29" s="11"/>
       <c r="K29" t="str">
         <f>IFERROR(VLOOKUP(J29,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L29" s="11"/>
-    </row>
-    <row r="30" spans="2:12">
+    </row>
+    <row r="30" spans="2:11">
       <c r="B30" t="str">
         <f>IFERROR(VLOOKUP(A30,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3682,14 +3628,12 @@
         <f>IFERROR(VLOOKUP(F30,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H30" s="11"/>
       <c r="K30" t="str">
         <f>IFERROR(VLOOKUP(J30,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L30" s="11"/>
-    </row>
-    <row r="31" spans="2:12">
+    </row>
+    <row r="31" spans="2:11">
       <c r="B31" t="str">
         <f>IFERROR(VLOOKUP(A31,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3706,14 +3650,12 @@
         <f>IFERROR(VLOOKUP(F31,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H31" s="11"/>
       <c r="K31" t="str">
         <f>IFERROR(VLOOKUP(J31,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L31" s="11"/>
-    </row>
-    <row r="32" spans="2:12">
+    </row>
+    <row r="32" spans="2:11">
       <c r="B32" t="str">
         <f>IFERROR(VLOOKUP(A32,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3730,14 +3672,12 @@
         <f>IFERROR(VLOOKUP(F32,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H32" s="11"/>
       <c r="K32" t="str">
         <f>IFERROR(VLOOKUP(J32,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L32" s="11"/>
-    </row>
-    <row r="33" spans="2:12">
+    </row>
+    <row r="33" spans="2:11">
       <c r="B33" t="str">
         <f>IFERROR(VLOOKUP(A33,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3754,14 +3694,12 @@
         <f>IFERROR(VLOOKUP(F33,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H33" s="11"/>
       <c r="K33" t="str">
         <f>IFERROR(VLOOKUP(J33,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L33" s="11"/>
-    </row>
-    <row r="34" spans="2:12">
+    </row>
+    <row r="34" spans="2:11">
       <c r="B34" t="str">
         <f>IFERROR(VLOOKUP(A34,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3778,14 +3716,12 @@
         <f>IFERROR(VLOOKUP(F34,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H34" s="11"/>
       <c r="K34" t="str">
         <f>IFERROR(VLOOKUP(J34,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L34" s="11"/>
-    </row>
-    <row r="35" spans="2:12">
+    </row>
+    <row r="35" spans="2:11">
       <c r="B35" t="str">
         <f>IFERROR(VLOOKUP(A35,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3802,14 +3738,12 @@
         <f>IFERROR(VLOOKUP(F35,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H35" s="11"/>
       <c r="K35" t="str">
         <f>IFERROR(VLOOKUP(J35,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L35" s="11"/>
-    </row>
-    <row r="36" spans="2:12">
+    </row>
+    <row r="36" spans="2:11">
       <c r="B36" t="str">
         <f>IFERROR(VLOOKUP(A36,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3826,14 +3760,12 @@
         <f>IFERROR(VLOOKUP(F36,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H36" s="11"/>
       <c r="K36" t="str">
         <f>IFERROR(VLOOKUP(J36,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L36" s="11"/>
-    </row>
-    <row r="37" spans="2:12">
+    </row>
+    <row r="37" spans="2:11">
       <c r="B37" t="str">
         <f>IFERROR(VLOOKUP(A37,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3850,14 +3782,12 @@
         <f>IFERROR(VLOOKUP(F37,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H37" s="11"/>
       <c r="K37" t="str">
         <f>IFERROR(VLOOKUP(J37,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L37" s="11"/>
-    </row>
-    <row r="38" spans="2:12">
+    </row>
+    <row r="38" spans="2:11">
       <c r="B38" t="str">
         <f>IFERROR(VLOOKUP(A38,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3874,14 +3804,12 @@
         <f>IFERROR(VLOOKUP(F38,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H38" s="11"/>
       <c r="K38" t="str">
         <f>IFERROR(VLOOKUP(J38,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L38" s="11"/>
-    </row>
-    <row r="39" spans="2:12">
+    </row>
+    <row r="39" spans="2:11">
       <c r="B39" t="str">
         <f>IFERROR(VLOOKUP(A39,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3898,14 +3826,12 @@
         <f>IFERROR(VLOOKUP(F39,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H39" s="11"/>
       <c r="K39" t="str">
         <f>IFERROR(VLOOKUP(J39,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L39" s="11"/>
-    </row>
-    <row r="40" spans="2:12">
+    </row>
+    <row r="40" spans="2:11">
       <c r="B40" t="str">
         <f>IFERROR(VLOOKUP(A40,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3922,14 +3848,12 @@
         <f>IFERROR(VLOOKUP(F40,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H40" s="11"/>
       <c r="K40" t="str">
         <f>IFERROR(VLOOKUP(J40,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L40" s="11"/>
-    </row>
-    <row r="41" spans="2:12">
+    </row>
+    <row r="41" spans="2:11">
       <c r="B41" t="str">
         <f>IFERROR(VLOOKUP(A41,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3946,14 +3870,12 @@
         <f>IFERROR(VLOOKUP(F41,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H41" s="11"/>
       <c r="K41" t="str">
         <f>IFERROR(VLOOKUP(J41,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L41" s="11"/>
-    </row>
-    <row r="42" spans="2:12">
+    </row>
+    <row r="42" spans="2:11">
       <c r="B42" t="str">
         <f>IFERROR(VLOOKUP(A42,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3970,14 +3892,12 @@
         <f>IFERROR(VLOOKUP(F42,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H42" s="11"/>
       <c r="K42" t="str">
         <f>IFERROR(VLOOKUP(J42,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L42" s="11"/>
-    </row>
-    <row r="43" spans="2:12">
+    </row>
+    <row r="43" spans="2:11">
       <c r="B43" t="str">
         <f>IFERROR(VLOOKUP(A43,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -3994,14 +3914,12 @@
         <f>IFERROR(VLOOKUP(F43,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H43" s="11"/>
       <c r="K43" t="str">
         <f>IFERROR(VLOOKUP(J43,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L43" s="11"/>
-    </row>
-    <row r="44" spans="2:12">
+    </row>
+    <row r="44" spans="2:11">
       <c r="B44" t="str">
         <f>IFERROR(VLOOKUP(A44,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -4018,14 +3936,12 @@
         <f>IFERROR(VLOOKUP(F44,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H44" s="11"/>
       <c r="K44" t="str">
         <f>IFERROR(VLOOKUP(J44,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L44" s="11"/>
-    </row>
-    <row r="45" spans="2:12">
+    </row>
+    <row r="45" spans="2:11">
       <c r="B45" t="str">
         <f>IFERROR(VLOOKUP(A45,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -4042,14 +3958,12 @@
         <f>IFERROR(VLOOKUP(F45,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H45" s="11"/>
       <c r="K45" t="str">
         <f>IFERROR(VLOOKUP(J45,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L45" s="11"/>
-    </row>
-    <row r="46" spans="2:12">
+    </row>
+    <row r="46" spans="2:11">
       <c r="B46" t="str">
         <f>IFERROR(VLOOKUP(A46,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -4066,14 +3980,12 @@
         <f>IFERROR(VLOOKUP(F46,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H46" s="11"/>
       <c r="K46" t="str">
         <f>IFERROR(VLOOKUP(J46,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L46" s="11"/>
-    </row>
-    <row r="47" spans="2:12">
+    </row>
+    <row r="47" spans="2:11">
       <c r="B47" t="str">
         <f>IFERROR(VLOOKUP(A47,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -4090,14 +4002,12 @@
         <f>IFERROR(VLOOKUP(F47,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H47" s="11"/>
       <c r="K47" t="str">
         <f>IFERROR(VLOOKUP(J47,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L47" s="11"/>
-    </row>
-    <row r="48" spans="2:12">
+    </row>
+    <row r="48" spans="2:11">
       <c r="B48" t="str">
         <f>IFERROR(VLOOKUP(A48,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -4114,14 +4024,12 @@
         <f>IFERROR(VLOOKUP(F48,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H48" s="11"/>
       <c r="K48" t="str">
         <f>IFERROR(VLOOKUP(J48,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L48" s="11"/>
-    </row>
-    <row r="49" spans="2:12">
+    </row>
+    <row r="49" spans="2:11">
       <c r="B49" t="str">
         <f>IFERROR(VLOOKUP(A49,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -4138,14 +4046,12 @@
         <f>IFERROR(VLOOKUP(F49,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H49" s="11"/>
       <c r="K49" t="str">
         <f>IFERROR(VLOOKUP(J49,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L49" s="11"/>
-    </row>
-    <row r="50" spans="2:12">
+    </row>
+    <row r="50" spans="2:11">
       <c r="B50" t="str">
         <f>IFERROR(VLOOKUP(A50,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -4162,14 +4068,12 @@
         <f>IFERROR(VLOOKUP(F50,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H50" s="11"/>
       <c r="K50" t="str">
         <f>IFERROR(VLOOKUP(J50,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L50" s="11"/>
-    </row>
-    <row r="51" spans="2:12">
+    </row>
+    <row r="51" spans="2:11">
       <c r="B51" t="str">
         <f>IFERROR(VLOOKUP(A51,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -4186,14 +4090,12 @@
         <f>IFERROR(VLOOKUP(F51,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H51" s="11"/>
       <c r="K51" t="str">
         <f>IFERROR(VLOOKUP(J51,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L51" s="11"/>
-    </row>
-    <row r="52" spans="2:12">
+    </row>
+    <row r="52" spans="2:11">
       <c r="B52" t="str">
         <f>IFERROR(VLOOKUP(A52,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -4210,14 +4112,12 @@
         <f>IFERROR(VLOOKUP(F52,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H52" s="11"/>
       <c r="K52" t="str">
         <f>IFERROR(VLOOKUP(J52,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L52" s="11"/>
-    </row>
-    <row r="53" spans="2:12">
+    </row>
+    <row r="53" spans="2:11">
       <c r="B53" t="str">
         <f>IFERROR(VLOOKUP(A53,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -4234,14 +4134,12 @@
         <f>IFERROR(VLOOKUP(F53,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H53" s="11"/>
       <c r="K53" t="str">
         <f>IFERROR(VLOOKUP(J53,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L53" s="11"/>
-    </row>
-    <row r="54" spans="2:12">
+    </row>
+    <row r="54" spans="2:11">
       <c r="B54" t="str">
         <f>IFERROR(VLOOKUP(A54,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -4258,14 +4156,12 @@
         <f>IFERROR(VLOOKUP(F54,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H54" s="11"/>
       <c r="K54" t="str">
         <f>IFERROR(VLOOKUP(J54,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L54" s="11"/>
-    </row>
-    <row r="55" spans="2:12">
+    </row>
+    <row r="55" spans="2:11">
       <c r="B55" t="str">
         <f>IFERROR(VLOOKUP(A55,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -4282,14 +4178,12 @@
         <f>IFERROR(VLOOKUP(F55,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H55" s="11"/>
       <c r="K55" t="str">
         <f>IFERROR(VLOOKUP(J55,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L55" s="11"/>
-    </row>
-    <row r="56" spans="2:12">
+    </row>
+    <row r="56" spans="2:11">
       <c r="B56" t="str">
         <f>IFERROR(VLOOKUP(A56,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -4306,14 +4200,12 @@
         <f>IFERROR(VLOOKUP(F56,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H56" s="11"/>
       <c r="K56" t="str">
         <f>IFERROR(VLOOKUP(J56,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L56" s="11"/>
-    </row>
-    <row r="57" spans="2:12">
+    </row>
+    <row r="57" spans="2:11">
       <c r="B57" t="str">
         <f>IFERROR(VLOOKUP(A57,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -4330,14 +4222,12 @@
         <f>IFERROR(VLOOKUP(F57,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H57" s="11"/>
       <c r="K57" t="str">
         <f>IFERROR(VLOOKUP(J57,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L57" s="11"/>
-    </row>
-    <row r="58" spans="2:12">
+    </row>
+    <row r="58" spans="2:11">
       <c r="B58" t="str">
         <f>IFERROR(VLOOKUP(A58,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -4354,14 +4244,12 @@
         <f>IFERROR(VLOOKUP(F58,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H58" s="11"/>
       <c r="K58" t="str">
         <f>IFERROR(VLOOKUP(J58,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L58" s="11"/>
-    </row>
-    <row r="59" spans="2:12">
+    </row>
+    <row r="59" spans="2:11">
       <c r="B59" t="str">
         <f>IFERROR(VLOOKUP(A59,venue!A:C,3,FALSE),"")</f>
         <v/>
@@ -4378,15 +4266,13 @@
         <f>IFERROR(VLOOKUP(F59,color!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="H59" s="11"/>
       <c r="K59" t="str">
         <f>IFERROR(VLOOKUP(J59,state!A:B,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L59" s="11"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="vcruljjcONbUpnrXd6NBi3/tFYnAw20d1EFcLILMB97chnTs9dfSw1BXpvTOGjf/eR2aixTaIBPDG20Kwg+mWw==" saltValue="7CY6YOfxRBDFKezRu0JAFg==" spinCount="100000" sheet="1" objects="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="c80Wkli/ZazN7IK51E/8LgTXPF+Hu8C1/7AmI5UELq3KJEpnZFZNGETLrbFS3U7iU7mFpgB4kqnm2B0mu0aloA==" saltValue="t7pZsr8COwoFKTC7OQhdng==" spinCount="100000" sheet="1" objects="1"/>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A59">
       <formula1>venue!$A$1:$A$276</formula1>
@@ -4408,7 +4294,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C276"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
@@ -7460,7 +7346,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="1"/>
   <cols>
@@ -7517,7 +7403,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="xsOmXkHveB4JhJsnvT4kpPwRMReV5BT3vCejhuK5l25e6RcaeM3TWGrUufPFCpGKtHgo0HdI4yTcK5vCwFpv2w==" saltValue="m9jJ287xcofTH5b5xpNhGA==" spinCount="100000" sheet="1" objects="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -7525,7 +7410,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="1"/>
   <cols>
@@ -7565,7 +7450,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="1"/>
   <sheetData>
